--- a/objects/n_by_adjustment_set.xlsx
+++ b/objects/n_by_adjustment_set.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t xml:space="preserve">type</t>
   </si>
@@ -60,6 +60,9 @@
   </si>
   <si>
     <t xml:space="preserve">n_surg_only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n_any</t>
   </si>
   <si>
     <t xml:space="preserve">n_skin</t>
@@ -564,13 +567,13 @@
         <v>0</v>
       </c>
       <c r="C10" t="n">
-        <v>1958</v>
+        <v>11799</v>
       </c>
       <c r="D10" t="n">
-        <v>1784</v>
+        <v>10479</v>
       </c>
       <c r="E10" t="n">
-        <v>1756</v>
+        <v>10215</v>
       </c>
     </row>
     <row r="11">
@@ -581,13 +584,13 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>2410</v>
+        <v>1958</v>
       </c>
       <c r="D11" t="n">
-        <v>2154</v>
+        <v>1784</v>
       </c>
       <c r="E11" t="n">
-        <v>2091</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="12">
@@ -598,13 +601,13 @@
         <v>0</v>
       </c>
       <c r="C12" t="n">
-        <v>1276</v>
+        <v>2410</v>
       </c>
       <c r="D12" t="n">
-        <v>1145</v>
+        <v>2154</v>
       </c>
       <c r="E12" t="n">
-        <v>1112</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="13">
@@ -615,13 +618,13 @@
         <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>1058</v>
+        <v>1276</v>
       </c>
       <c r="D13" t="n">
-        <v>908</v>
+        <v>1145</v>
       </c>
       <c r="E13" t="n">
-        <v>882</v>
+        <v>1112</v>
       </c>
     </row>
     <row r="14">
@@ -632,12 +635,29 @@
         <v>0</v>
       </c>
       <c r="C14" t="n">
+        <v>1058</v>
+      </c>
+      <c r="D14" t="n">
+        <v>908</v>
+      </c>
+      <c r="E14" t="n">
+        <v>882</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>21</v>
+      </c>
+      <c r="B15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C15" t="n">
         <v>459</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D15" t="n">
         <v>392</v>
       </c>
-      <c r="E14" t="n">
+      <c r="E15" t="n">
         <v>377</v>
       </c>
     </row>

--- a/objects/n_by_adjustment_set.xlsx
+++ b/objects/n_by_adjustment_set.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t xml:space="preserve">type</t>
   </si>
@@ -78,6 +78,39 @@
   </si>
   <si>
     <t xml:space="preserve">n_lung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nr_chemo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">recent_treatment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nr_rad_only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nr_surg_only</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nr_any</t>
+  </si>
+  <si>
+    <t xml:space="preserve">recent_type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nr_skin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nr_heme</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nr_breast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nr_prostate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nr_lung</t>
   </si>
 </sst>
 </file>
@@ -661,6 +694,159 @@
         <v>377</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>22</v>
+      </c>
+      <c r="B16" t="s">
+        <v>23</v>
+      </c>
+      <c r="C16" t="n">
+        <v>2653</v>
+      </c>
+      <c r="D16" t="n">
+        <v>2340</v>
+      </c>
+      <c r="E16" t="n">
+        <v>2284</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>24</v>
+      </c>
+      <c r="B17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17" t="n">
+        <v>534</v>
+      </c>
+      <c r="D17" t="n">
+        <v>475</v>
+      </c>
+      <c r="E17" t="n">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>25</v>
+      </c>
+      <c r="B18" t="s">
+        <v>23</v>
+      </c>
+      <c r="C18" t="n">
+        <v>34</v>
+      </c>
+      <c r="D18" t="n">
+        <v>32</v>
+      </c>
+      <c r="E18" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" t="s">
+        <v>27</v>
+      </c>
+      <c r="C19" t="n">
+        <v>5369</v>
+      </c>
+      <c r="D19" t="n">
+        <v>4640</v>
+      </c>
+      <c r="E19" t="n">
+        <v>4497</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>28</v>
+      </c>
+      <c r="B20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" t="n">
+        <v>729</v>
+      </c>
+      <c r="D20" t="n">
+        <v>644</v>
+      </c>
+      <c r="E20" t="n">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" t="s">
+        <v>27</v>
+      </c>
+      <c r="C21" t="n">
+        <v>964</v>
+      </c>
+      <c r="D21" t="n">
+        <v>827</v>
+      </c>
+      <c r="E21" t="n">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>30</v>
+      </c>
+      <c r="B22" t="s">
+        <v>27</v>
+      </c>
+      <c r="C22" t="n">
+        <v>437</v>
+      </c>
+      <c r="D22" t="n">
+        <v>381</v>
+      </c>
+      <c r="E22" t="n">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" t="s">
+        <v>27</v>
+      </c>
+      <c r="C23" t="n">
+        <v>447</v>
+      </c>
+      <c r="D23" t="n">
+        <v>373</v>
+      </c>
+      <c r="E23" t="n">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>32</v>
+      </c>
+      <c r="B24" t="s">
+        <v>27</v>
+      </c>
+      <c r="C24" t="n">
+        <v>219</v>
+      </c>
+      <c r="D24" t="n">
+        <v>181</v>
+      </c>
+      <c r="E24" t="n">
+        <v>174</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
